--- a/outputs/tables/Regression_Results_Pooled_DistrictCluster.xlsx
+++ b/outputs/tables/Regression_Results_Pooled_DistrictCluster.xlsx
@@ -430,178 +430,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
+          <t>Outcome: Delta log NL = log(NL_t) - log(NL_{t-1}) (year-on-year growth in night-light radiance).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Source files</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>master_dataset_T_clean.csv + master_dataset_T_minus_1_clean.csv</t>
+          <t>Lagged regressors: NDVI_{t-1}, NDBI_{t-1}. Flood (Seasonal_Ratio) is contemporaneous.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sample scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>All states (BIHAR, JHARKHAND, ORISSA, WEST BENGAL), 2015-2019</t>
+          <t>Two-way FE: AC (entity) + YEAR (time). Constant is explicit; entity/time effects absorbed by PanelOLS.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Why 2014 dropped</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Outcome requires NL_{t-1}; 2013 not in panel</t>
+          <t>SEs clustered by district (ST_CODE_DT_CODE). Significance: *** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Median outcome</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>log(NL_median_t) - log(NL_median_{t-1})</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mean outcome</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>log(NL_mean_t) - log(NL_mean_{t-1})</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Seasonal_Ratio</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>contemporaneous (t)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NDVI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lagged (t-1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NDBI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lagged (t-1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fixed effects</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AC (UNIT_ID) + YEAR — two-way absorbed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Std errors</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clustered by DISTRICT (ST_CODE_DT_CODE), n=108 clusters</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Note on clustering</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Slope coefficients are identical to the AC-clustered run; only SEs (and therefore t-stats, p-values, CIs, significance) change. Fewer clusters =&gt; generally less precision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Significance</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
+          <t>Cross-check: same specification as run_nl_ols_pooled.py (pyfixest); coefficients should be close.</t>
         </is>
       </c>
     </row>
@@ -616,17 +486,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -641,25 +502,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Median_SE</t>
+          <t>Median_Sig</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Median_Sig</t>
+          <t>Mean_Coef</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mean_Coef</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Mean_SE</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mean_Sig</t>
         </is>
@@ -672,23 +523,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.349055</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.171475</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>-0.3406</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>p &lt; 0.05</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>-0.486996</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.197399</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>-0.4746</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>p &lt; 0.05</t>
         </is>
@@ -701,23 +546,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.060751</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.082894</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>-0.0619</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>-0.109585</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.085171</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>-0.1112</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -730,17 +569,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.140045</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.678011</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>1.1235</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>p &lt; 0.10</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>1.2768</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -753,85 +592,20 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.15388</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.108327</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>-1.133</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>-1.8619</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Observations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3890</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3890</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ACs (entities)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>778</v>
-      </c>
-      <c r="E7" t="n">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Districts (clusters)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>108</v>
-      </c>
-      <c r="E8" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R-sq (within)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0444</v>
       </c>
     </row>
   </sheetData>
@@ -847,17 +621,6 @@
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -918,22 +681,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.349055</v>
+        <v>-0.3406002977173866</v>
       </c>
       <c r="D2" t="n">
-        <v>0.171475</v>
+        <v>0.1692093538801186</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.035597</v>
+        <v>-2.012892844911488</v>
       </c>
       <c r="F2" t="n">
-        <v>0.041876</v>
+        <v>0.04421168086991045</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.685271</v>
+        <v>-0.6723732847331563</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.012838</v>
+        <v>-0.008827310701616964</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -953,22 +716,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.060751</v>
+        <v>-0.06192569670750594</v>
       </c>
       <c r="D3" t="n">
-        <v>0.082894</v>
+        <v>0.08190465067369813</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.732873</v>
+        <v>-0.7560705796086375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.463691</v>
+        <v>0.4496639783024095</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.223284</v>
+        <v>-0.2225181815872015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.101782</v>
+        <v>0.09866678817218963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -988,22 +751,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.140045</v>
+        <v>1.123502152439795</v>
       </c>
       <c r="D4" t="n">
-        <v>0.678011</v>
+        <v>0.6755296859507508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.681455</v>
+        <v>1.663142532157652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.092775</v>
+        <v>0.09638437641865627</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.189351</v>
+        <v>-0.201025697743308</v>
       </c>
       <c r="H4" t="n">
-        <v>2.469442</v>
+        <v>2.448030002622898</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1023,22 +786,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.15388</v>
+        <v>-1.132983102181955</v>
       </c>
       <c r="D5" t="n">
-        <v>1.108327</v>
+        <v>1.101773570667614</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.041101</v>
+        <v>-1.028326629304994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.29791</v>
+        <v>0.3038759471721133</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.327007</v>
+        <v>-3.293257934354656</v>
       </c>
       <c r="H5" t="n">
-        <v>1.019248</v>
+        <v>1.027291729990747</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1059,10 +822,6 @@
   </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1096,7 +855,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>log(NL_median_t) - log(NL_median_{t-1}) = b0 + b1*Seasonal_Ratio_it + b2*NDVI_median_{i,t-1} + b3*NDBI_median_{i,t-1} + alpha_i + gamma_t + eps_it</t>
+          <t>log(NL_median)_t - log(NL_median)_(t-1) = b0 + b1*Seasonal_Ratio + b2*NDVI_median_(t-1) + b3*NDBI_median_(t-1) + a_i + g_t + e_it</t>
         </is>
       </c>
     </row>
@@ -1108,7 +867,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Two-way FE (PanelOLS) with explicit constant</t>
+          <t>Two-way FE (linearmodels PanelOLS) — cross-check of pyfixest primary</t>
         </is>
       </c>
     </row>
@@ -1120,7 +879,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AC (UNIT_ID) — alpha_i</t>
+          <t>AC (AC_UID) = alpha_i</t>
         </is>
       </c>
     </row>
@@ -1132,7 +891,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YEAR — gamma_t</t>
+          <t>YEAR = gamma_t</t>
         </is>
       </c>
     </row>
@@ -1165,7 +924,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>778</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10">
@@ -1185,7 +944,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.026742</v>
+        <v>0.02609599688365805</v>
       </c>
     </row>
     <row r="12">
@@ -1195,7 +954,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.555835</v>
+        <v>-0.5186113025407009</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +964,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.118182</v>
+        <v>-0.1132515573486446</v>
       </c>
     </row>
     <row r="14">
@@ -1215,7 +974,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3227</v>
+        <v>3.306722150523054</v>
       </c>
     </row>
     <row r="15">
@@ -1225,7 +984,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.018965</v>
+        <v>0.01938220575527416</v>
       </c>
     </row>
   </sheetData>
@@ -1241,17 +1000,6 @@
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1312,22 +1060,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.486996</v>
+        <v>-0.4746355139037859</v>
       </c>
       <c r="D2" t="n">
-        <v>0.197399</v>
+        <v>0.1953920663208561</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.467068</v>
+        <v>-2.429144247465914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.013676</v>
+        <v>0.01519063630728179</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.874041</v>
+        <v>-0.8577455961536217</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.099951</v>
+        <v>-0.09152543165395011</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1347,22 +1095,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.109585</v>
+        <v>-0.1111841371066869</v>
       </c>
       <c r="D3" t="n">
-        <v>0.085171</v>
+        <v>0.0842021194746375</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.286654</v>
+        <v>-1.320443449647092</v>
       </c>
       <c r="F3" t="n">
-        <v>0.198311</v>
+        <v>0.1867838891635547</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.276582</v>
+        <v>-0.276281326183783</v>
       </c>
       <c r="H3" t="n">
-        <v>0.057411</v>
+        <v>0.05391305197040915</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1382,22 +1130,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.29835</v>
+        <v>1.276819292443545</v>
       </c>
       <c r="D4" t="n">
-        <v>0.920378</v>
+        <v>0.9184727711329241</v>
       </c>
       <c r="E4" t="n">
-        <v>1.41067</v>
+        <v>1.390154757520579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.158442</v>
+        <v>0.1645810841810937</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.506261</v>
+        <v>-0.5240531048786077</v>
       </c>
       <c r="H4" t="n">
-        <v>3.102961</v>
+        <v>3.077691689765698</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1417,22 +1165,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.898889</v>
+        <v>-1.861931833187922</v>
       </c>
       <c r="D5" t="n">
-        <v>1.357085</v>
+        <v>1.350149751056613</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.399242</v>
+        <v>-1.379055791204489</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16184</v>
+        <v>0.1679764331304856</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.559763</v>
+        <v>-4.50920401734867</v>
       </c>
       <c r="H5" t="n">
-        <v>0.761985</v>
+        <v>0.7853403509728256</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1453,10 +1201,6 @@
   </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1490,7 +1234,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>log(NL_mean_t) - log(NL_mean_{t-1}) = b0 + b1*Seasonal_Ratio_it + b2*NDVI_mean_{i,t-1} + b3*NDBI_mean_{i,t-1} + alpha_i + gamma_t + eps_it</t>
+          <t>log(NL_mean)_t - log(NL_mean)_(t-1) = b0 + b1*Seasonal_Ratio + b2*NDVI_mean_(t-1) + b3*NDBI_mean_(t-1) + a_i + g_t + e_it</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1246,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Two-way FE (PanelOLS) with explicit constant</t>
+          <t>Two-way FE (linearmodels PanelOLS) — cross-check of pyfixest primary</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1258,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AC (UNIT_ID) — alpha_i</t>
+          <t>AC (AC_UID) = alpha_i</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1270,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YEAR — gamma_t</t>
+          <t>YEAR = gamma_t</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1303,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>778</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1323,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04435</v>
+        <v>0.04323722591745394</v>
       </c>
     </row>
     <row r="12">
@@ -1589,7 +1333,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.866517</v>
+        <v>-0.811151335692049</v>
       </c>
     </row>
     <row r="13">
@@ -1599,7 +1343,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.19527</v>
+        <v>-0.1865389715573806</v>
       </c>
     </row>
     <row r="14">
@@ -1609,7 +1353,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.0804</v>
+        <v>5.026263573430225</v>
       </c>
     </row>
     <row r="15">
@@ -1619,7 +1363,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001649</v>
+        <v>0.001778704215857463</v>
       </c>
     </row>
   </sheetData>
